--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDE3E736-650A-4250-B521-BBB2160A8AEA}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C57537A-7648-4169-B49D-70E30B33CB95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="11170" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>8.1977753488073034E-3</v>
+        <v>8.6799974281489087E-3</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>12.75</v>
+        <v>13.5</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>12.75</v>
+        <v>13.5</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>7.0735090152565877E-2</v>
+        <v>7.4895977808599162E-2</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>12.75</v>
+        <v>13.5</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>8.1977753488073034E-3</v>
+        <v>8.6799974281489087E-3</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>12.75</v>
+        <v>13.5</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>7.0735090152565877E-2</v>
+        <v>7.4895977808599162E-2</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7657,10 +7657,14 @@
         <v>0.75</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I17" s="33">
+        <v>46301</v>
+      </c>
+      <c r="J17" s="34">
+        <v>1</v>
+      </c>
       <c r="K17" s="35"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C57537A-7648-4169-B49D-70E30B33CB95}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{099C62A9-ED81-4289-BBD2-A3164DD8CEA1}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="11170" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>8.6799974281489087E-3</v>
+        <v>9.6444415868321212E-3</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>7.4895977808599162E-2</v>
+        <v>8.3217753120665747E-2</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>8.6799974281489087E-3</v>
+        <v>9.6444415868321212E-3</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>7.4895977808599162E-2</v>
+        <v>8.3217753120665747E-2</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7690,10 +7690,14 @@
         <v>1.5</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I18" s="33">
+        <v>46304</v>
+      </c>
+      <c r="J18" s="34">
+        <v>1</v>
+      </c>
       <c r="K18" s="35"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{099C62A9-ED81-4289-BBD2-A3164DD8CEA1}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92F8D26C-7EAB-41FB-8297-853CF954EA0B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>9.6444415868321212E-3</v>
+        <v>1.0930367131743071E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>11.25</v>
+        <v>12.75</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>8.3217753120665747E-2</v>
+        <v>9.4313453536754507E-2</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>11.25</v>
+        <v>12.75</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>9.6444415868321212E-3</v>
+        <v>1.0930367131743071E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>11.25</v>
+        <v>12.75</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>8.3217753120665747E-2</v>
+        <v>9.4313453536754507E-2</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7723,10 +7723,14 @@
         <v>1</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="33"/>
-      <c r="J19" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I19" s="33">
+        <v>46304</v>
+      </c>
+      <c r="J19" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K19" s="35"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -7752,10 +7756,14 @@
         <v>1</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I20" s="33"/>
-      <c r="J20" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I20" s="33">
+        <v>46305</v>
+      </c>
+      <c r="J20" s="34">
+        <v>1</v>
+      </c>
       <c r="K20" s="35"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92F8D26C-7EAB-41FB-8297-853CF954EA0B}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB0D01E8-C9B8-49C6-8DC4-6DA1D817202A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.0930367131743071E-2</v>
+        <v>1.1251848517970809E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>9.4313453536754507E-2</v>
+        <v>9.7087378640776698E-2</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.0930367131743071E-2</v>
+        <v>1.1251848517970809E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>9.4313453536754507E-2</v>
+        <v>9.7087378640776698E-2</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7789,10 +7789,14 @@
         <v>0.5</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I21" s="33"/>
-      <c r="J21" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I21" s="33">
+        <v>46305</v>
+      </c>
+      <c r="J21" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K21" s="35"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB0D01E8-C9B8-49C6-8DC4-6DA1D817202A}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACF3AE54-C2CC-4E6A-9B7A-3AE71008BBD5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.1251848517970809E-2</v>
+        <v>1.1573329904198546E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>9.7087378640776698E-2</v>
+        <v>9.9861303744798888E-2</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.1251848517970809E-2</v>
+        <v>1.1573329904198546E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>9.7087378640776698E-2</v>
+        <v>9.9861303744798888E-2</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7822,10 +7822,14 @@
         <v>0.5</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I22" s="33">
+        <v>46306</v>
+      </c>
+      <c r="J22" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K22" s="35"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACF3AE54-C2CC-4E6A-9B7A-3AE71008BBD5}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D124FDD7-74D3-4A7A-9525-D364791A9C7B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.1573329904198546E-2</v>
+        <v>1.2055551983540152E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>13.75</v>
+        <v>14.5</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>9.9861303744798888E-2</v>
+        <v>0.10402219140083217</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>13.75</v>
+        <v>14.5</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.1573329904198546E-2</v>
+        <v>1.2055551983540152E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>13.75</v>
+        <v>14.5</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>9.9861303744798888E-2</v>
+        <v>0.10402219140083217</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7855,10 +7855,14 @@
         <v>0.75</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I23" s="33"/>
-      <c r="J23" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I23" s="33">
+        <v>46306</v>
+      </c>
+      <c r="J23" s="34">
+        <v>0.75</v>
+      </c>
       <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D124FDD7-74D3-4A7A-9525-D364791A9C7B}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302006B5-47CC-42DA-A351-E927F7BF88CA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1110">
   <si>
     <t>Teach Yourself CS — Progress Dashboard</t>
   </si>
@@ -3384,9 +3384,6 @@
   </si>
   <si>
     <t>Done</t>
-  </si>
-  <si>
-    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -4202,11 +4199,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.2055551983540152E-2</v>
+        <v>1.6877772776956214E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>18.75</v>
+        <v>26.25</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4211,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4282,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>18.75</v>
+        <v>26.25</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.10402219140083217</v>
+        <v>0.14563106796116504</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4294,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4306,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4314,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4773,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>18.75</v>
+        <v>26.25</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.2055551983540152E-2</v>
+        <v>1.6877772776956214E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4785,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4797,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4805,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7223,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>18.75</v>
+        <v>26.25</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.10402219140083217</v>
+        <v>0.14563106796116504</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7496,10 +7493,14 @@
         <v>6</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>1110</v>
-      </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I12" s="33">
+        <v>46308</v>
+      </c>
+      <c r="J12" s="34">
+        <v>5</v>
+      </c>
       <c r="K12" s="35"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -7888,10 +7889,14 @@
         <v>1.5</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I24" s="33"/>
-      <c r="J24" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I24" s="33">
+        <v>46308</v>
+      </c>
+      <c r="J24" s="34">
+        <v>1.5</v>
+      </c>
       <c r="K24" s="35"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302006B5-47CC-42DA-A351-E927F7BF88CA}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14CCD6DF-70E9-4110-AC71-CC56674FC43E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1111">
   <si>
     <t>Teach Yourself CS — Progress Dashboard</t>
   </si>
@@ -3384,6 +3384,9 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -4199,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.6877772776956214E-2</v>
+        <v>1.7520735549411685E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4211,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4282,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.14563106796116504</v>
+        <v>0.15117891816920942</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4294,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4306,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4314,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4773,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.6877772776956214E-2</v>
+        <v>1.7520735549411685E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4785,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4797,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4805,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7223,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.14563106796116504</v>
+        <v>0.15117891816920942</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7918,7 +7921,7 @@
         <v>4</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>135</v>
+        <v>1110</v>
       </c>
       <c r="I25" s="33"/>
       <c r="J25" s="34"/>
@@ -7947,10 +7950,14 @@
         <v>1</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I26" s="33"/>
-      <c r="J26" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I26" s="33">
+        <v>46312</v>
+      </c>
+      <c r="J26" s="34">
+        <v>1</v>
+      </c>
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14CCD6DF-70E9-4110-AC71-CC56674FC43E}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67561093-5D57-4F38-888A-0A38E6614D58}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.7520735549411685E-2</v>
+        <v>1.7842216935639425E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>27.25</v>
+        <v>27.75</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>27.25</v>
+        <v>27.75</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.15117891816920942</v>
+        <v>0.15395284327323161</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>27.25</v>
+        <v>27.75</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.7520735549411685E-2</v>
+        <v>1.7842216935639425E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>27.25</v>
+        <v>27.75</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.15117891816920942</v>
+        <v>0.15395284327323161</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7983,10 +7983,14 @@
         <v>0.5</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I27" s="33"/>
-      <c r="J27" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I27" s="33">
+        <v>46312</v>
+      </c>
+      <c r="J27" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67561093-5D57-4F38-888A-0A38E6614D58}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A887A957-CD8E-4821-A6D2-734643D7F198}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.7842216935639425E-2</v>
+        <v>1.84851797080949E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.15395284327323161</v>
+        <v>0.15950069348127602</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.7842216935639425E-2</v>
+        <v>1.84851797080949E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.15395284327323161</v>
+        <v>0.15950069348127602</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -8016,10 +8016,14 @@
         <v>1</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I28" s="33"/>
-      <c r="J28" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I28" s="33">
+        <v>46312</v>
+      </c>
+      <c r="J28" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A887A957-CD8E-4821-A6D2-734643D7F198}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92979A8-37CE-4D65-AA43-D7E071E634EC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.84851797080949E-2</v>
+        <v>1.8967401787436507E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>28.75</v>
+        <v>29.5</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>23</v>
+        <v>23.75</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>28.75</v>
+        <v>29.5</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.15950069348127602</v>
+        <v>0.1636615811373093</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>23</v>
+        <v>23.75</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>28.75</v>
+        <v>29.5</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.84851797080949E-2</v>
+        <v>1.8967401787436507E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>23</v>
+        <v>23.75</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>28.75</v>
+        <v>29.5</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.15950069348127602</v>
+        <v>0.1636615811373093</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -8049,10 +8049,14 @@
         <v>0.75</v>
       </c>
       <c r="H29" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I29" s="33"/>
-      <c r="J29" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I29" s="33">
+        <v>46313</v>
+      </c>
+      <c r="J29" s="34">
+        <v>0.75</v>
+      </c>
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92979A8-37CE-4D65-AA43-D7E071E634EC}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC7BB71B-E083-482E-8670-A74BB51DB979}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.8967401787436507E-2</v>
+        <v>1.9128142480550375E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>29.5</v>
+        <v>29.75</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>23.75</v>
+        <v>24</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>29.5</v>
+        <v>29.75</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.1636615811373093</v>
+        <v>0.1650485436893204</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>23.75</v>
+        <v>24</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>29.5</v>
+        <v>29.75</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.8967401787436507E-2</v>
+        <v>1.9128142480550375E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>23.75</v>
+        <v>24</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>29.5</v>
+        <v>29.75</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.1636615811373093</v>
+        <v>0.1650485436893204</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -8082,10 +8082,14 @@
         <v>0.25</v>
       </c>
       <c r="H30" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I30" s="33"/>
-      <c r="J30" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I30" s="33">
+        <v>46318</v>
+      </c>
+      <c r="J30" s="34">
+        <v>0.25</v>
+      </c>
       <c r="K30" s="35"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -8111,7 +8115,7 @@
         <v>0.5</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>135</v>
+        <v>1110</v>
       </c>
       <c r="I31" s="33"/>
       <c r="J31" s="34"/>

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC7BB71B-E083-482E-8670-A74BB51DB979}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81C44E89-901D-44A5-8A75-2A086645A005}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1110">
   <si>
     <t>Teach Yourself CS — Progress Dashboard</t>
   </si>
@@ -3384,9 +3384,6 @@
   </si>
   <si>
     <t>Done</t>
-  </si>
-  <si>
-    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -4202,11 +4199,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>1.9128142480550375E-2</v>
+        <v>2.3468141194624828E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>29.75</v>
+        <v>36.5</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4211,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>24</v>
+        <v>29.75</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4282,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>29.75</v>
+        <v>36.5</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.1650485436893204</v>
+        <v>0.20249653259361997</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4294,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4306,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>24</v>
+        <v>29.75</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4317,7 +4314,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4776,11 +4773,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>29.75</v>
+        <v>36.5</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>1.9128142480550375E-2</v>
+        <v>2.3468141194624828E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4785,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4797,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>24</v>
+        <v>29.75</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4808,7 +4805,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46318</v>
+        <v>46322</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7226,21 +7223,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>29.75</v>
+        <v>36.5</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.1650485436893204</v>
+        <v>0.20249653259361997</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -7921,10 +7918,14 @@
         <v>4</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>1110</v>
-      </c>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I25" s="33">
+        <v>46322</v>
+      </c>
+      <c r="J25" s="34">
+        <v>4</v>
+      </c>
       <c r="K25" s="35"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -8115,10 +8116,14 @@
         <v>0.5</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>1110</v>
-      </c>
-      <c r="I31" s="33"/>
-      <c r="J31" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I31" s="33">
+        <v>46322</v>
+      </c>
+      <c r="J31" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K31" s="35"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -8144,10 +8149,14 @@
         <v>1</v>
       </c>
       <c r="H32" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I32" s="33">
+        <v>46322</v>
+      </c>
+      <c r="J32" s="34">
+        <v>0.75</v>
+      </c>
       <c r="K32" s="35"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -8173,10 +8182,14 @@
         <v>0.5</v>
       </c>
       <c r="H33" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I33" s="33"/>
-      <c r="J33" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I33" s="33">
+        <v>46322</v>
+      </c>
+      <c r="J33" s="34">
+        <v>0.25</v>
+      </c>
       <c r="K33" s="35"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -8202,10 +8215,14 @@
         <v>0.75</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I34" s="33"/>
-      <c r="J34" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I34" s="33">
+        <v>46322</v>
+      </c>
+      <c r="J34" s="34">
+        <v>0.25</v>
+      </c>
       <c r="K34" s="35"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81C44E89-901D-44A5-8A75-2A086645A005}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57706BA9-580F-4954-97C7-903A47CF320D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="1111">
   <si>
     <t>Teach Yourself CS — Progress Dashboard</t>
   </si>
@@ -3384,6 +3384,9 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -4199,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>2.3468141194624828E-2</v>
+        <v>2.587925159133286E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>36.5</v>
+        <v>40.25</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4211,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>29.75</v>
+        <v>33</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4282,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>36.5</v>
+        <v>40.25</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.20249653259361997</v>
+        <v>0.22330097087378642</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4294,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4306,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>29.75</v>
+        <v>33</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4314,7 +4317,7 @@
       </c>
       <c r="M8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MAX('1 Programming'!$I$6:$I$500))</f>
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="N8" s="7" t="str">
         <f>IF(AND(D8&gt;0,E8&gt;=D8-0.001),"Complete",IF(OR(E8&gt;0,COUNTIF('1 Programming'!$H$6:$H$500,"In progress")&gt;0),"In progress","Not started"))</f>
@@ -4773,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>36.5</v>
+        <v>40.25</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>2.3468141194624828E-2</v>
+        <v>2.587925159133286E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4785,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4797,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>29.75</v>
+        <v>33</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -4805,7 +4808,7 @@
       </c>
       <c r="M17" s="17">
         <f>IF(COUNT(M8:M16)=0,"",MAX(M8:M16))</f>
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>COUNTIF(N8:N16,"Complete")&amp;" of 9 complete"</f>
@@ -7181,9 +7184,9 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="70" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
@@ -7223,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>36.5</v>
+        <v>40.25</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.20249653259361997</v>
+        <v>0.22330097087378642</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -8248,10 +8251,14 @@
         <v>0.25</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I35" s="33"/>
-      <c r="J35" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I35" s="33">
+        <v>46323</v>
+      </c>
+      <c r="J35" s="34">
+        <v>0.25</v>
+      </c>
       <c r="K35" s="35"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -8277,10 +8284,14 @@
         <v>0.5</v>
       </c>
       <c r="H36" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I36" s="33"/>
-      <c r="J36" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I36" s="33">
+        <v>46323</v>
+      </c>
+      <c r="J36" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K36" s="35"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -8306,10 +8317,14 @@
         <v>1.5</v>
       </c>
       <c r="H37" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I37" s="33"/>
-      <c r="J37" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I37" s="33">
+        <v>46324</v>
+      </c>
+      <c r="J37" s="34">
+        <v>1.25</v>
+      </c>
       <c r="K37" s="35"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -8335,10 +8350,14 @@
         <v>1</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I38" s="33"/>
-      <c r="J38" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I38" s="33">
+        <v>46324</v>
+      </c>
+      <c r="J38" s="34">
+        <v>0.75</v>
+      </c>
       <c r="K38" s="35"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -8360,7 +8379,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="32" t="s">
-        <v>135</v>
+        <v>1110</v>
       </c>
       <c r="I39" s="33"/>
       <c r="J39" s="34"/>
@@ -8389,10 +8408,14 @@
         <v>0.5</v>
       </c>
       <c r="H40" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I40" s="33"/>
-      <c r="J40" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I40" s="33">
+        <v>46325</v>
+      </c>
+      <c r="J40" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K40" s="35"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57706BA9-580F-4954-97C7-903A47CF320D}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1B4318B-20BB-43C8-A3C0-B899FAD5BD50}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>2.587925159133286E-2</v>
+        <v>2.6522214363788335E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.22330097087378642</v>
+        <v>0.2288488210818308</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>2.587925159133286E-2</v>
+        <v>2.6522214363788335E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.22330097087378642</v>
+        <v>0.2288488210818308</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -8441,10 +8441,14 @@
         <v>1</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I41" s="33"/>
-      <c r="J41" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I41" s="33">
+        <v>46325</v>
+      </c>
+      <c r="J41" s="34">
+        <v>0.5</v>
+      </c>
       <c r="K41" s="35"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">

--- a/TYCS_Study_Plan_Tracker.xlsx
+++ b/TYCS_Study_Plan_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e990d687e3194b/Documents/TYCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1B4318B-20BB-43C8-A3C0-B899FAD5BD50}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{05A0118C-8117-4732-9D05-9B1B0E3931DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6E7E611-E3FA-451B-9938-43685256B385}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4202,11 +4202,11 @@
     <row r="5" spans="1:14" ht="20" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>F17</f>
-        <v>2.6522214363788335E-2</v>
+        <v>2.7004436443129939E-2</v>
       </c>
       <c r="D5" s="4">
         <f>E17</f>
-        <v>41.25</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4">
         <f>D17</f>
@@ -4214,11 +4214,11 @@
       </c>
       <c r="H5" s="4">
         <f>K17</f>
-        <v>33.5</v>
+        <v>34.25</v>
       </c>
       <c r="J5" s="5">
         <f>H17</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" s="5">
         <f>J17</f>
@@ -4285,11 +4285,11 @@
       </c>
       <c r="E8" s="10">
         <f>SUMIFS('1 Programming'!$G$6:$G$500,'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>41.25</v>
+        <v>42</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" ref="F8:F17" si="0">IF(D8=0,0,E8/D8)</f>
-        <v>0.2288488210818308</v>
+        <v>0.23300970873786409</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise")-SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H8" s="12">
         <f>SUMIFS('1 Programming'!$E$6:$E$500,'1 Programming'!$D$6:$D$500,"Exercise",'1 Programming'!$H$6:$H$500,"Done")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="12">
         <f>COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project")-COUNTIFS('1 Programming'!$D$6:$D$500,"Lab/Project",'1 Programming'!$H$6:$H$500,"Skipped")</f>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="K8" s="10">
         <f>SUM('1 Programming'!$J$6:$J$500)</f>
-        <v>33.5</v>
+        <v>34.25</v>
       </c>
       <c r="L8" s="13">
         <f>IF(COUNT('1 Programming'!$I$6:$I$500)=0,"",MIN('1 Programming'!$I$6:$I$500))</f>
@@ -4776,11 +4776,11 @@
       </c>
       <c r="E17" s="15">
         <f>SUM(E8:E16)</f>
-        <v>41.25</v>
+        <v>42</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
-        <v>2.6522214363788335E-2</v>
+        <v>2.7004436443129939E-2</v>
       </c>
       <c r="G17" s="14">
         <f>SUM(G8:G16)</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H17" s="14">
         <f>SUM(H8:H16)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="14">
         <f>SUM(I8:I16)</f>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="K17" s="15">
         <f>SUM(K8:K16)</f>
-        <v>33.5</v>
+        <v>34.25</v>
       </c>
       <c r="L17" s="17">
         <f>IF(COUNT(L8:L16)=0,"",MIN(L8:L16))</f>
@@ -7226,21 +7226,21 @@
       </c>
       <c r="D3" s="26">
         <f>SUMIFS($G$6:$G$500,$H$6:$H$500,"Done")</f>
-        <v>41.25</v>
+        <v>42</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="27">
         <f>IF(B3=0,0,D3/B3)</f>
-        <v>0.2288488210818308</v>
+        <v>0.23300970873786409</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="28">
         <f>SUMIFS($E$6:$E$500,$D$6:$D$500,"Exercise",$H$6:$H$500,"Done")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>123</v>
@@ -8474,10 +8474,14 @@
         <v>0.75</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I42" s="33"/>
-      <c r="J42" s="34"/>
+        <v>1109</v>
+      </c>
+      <c r="I42" s="33">
+        <v>46325</v>
+      </c>
+      <c r="J42" s="34">
+        <v>0.75</v>
+      </c>
       <c r="K42" s="35"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
